--- a/Adapter(Properties_2nd)/Adapterの学習資料.xlsx
+++ b/Adapter(Properties_2nd)/Adapterの学習資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokan\study\java\Design_Patterns\Adapter(Properties_2nd)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F27BC1A-F629-42EF-8FE9-E1DD587A7BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7ADCB55-F5D8-4F6F-9309-A53B81C3F17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="705" yWindow="1395" windowWidth="21345" windowHeight="13620" xr2:uid="{E008EE47-AA91-43C5-8CC9-6597E550809F}"/>
+    <workbookView xWindow="165" yWindow="900" windowWidth="21345" windowHeight="13620" xr2:uid="{E008EE47-AA91-43C5-8CC9-6597E550809F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1789,6 +1789,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{504824F7-6A3C-4AB5-AD59-B08BA8AA5113}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:R18"/>
   <sheetFormatPr defaultColWidth="5.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1820,6 +1823,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="82" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>